--- a/templates/employees_template.xlsx
+++ b/templates/employees_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AB74D1-ED41-40AB-B313-A9350026F90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7F6B30-D432-4524-BEF5-CE7DA56E5BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Nº Interno</t>
   </si>
@@ -123,21 +123,6 @@
     <t>BAIXA</t>
   </si>
   <si>
-    <t>FALTA INJUSTIFICADA</t>
-  </si>
-  <si>
-    <t>FALTA JUSTIFICADA</t>
-  </si>
-  <si>
-    <t>LIC. CASAMENTO</t>
-  </si>
-  <si>
-    <t>LIC. PARENTAL</t>
-  </si>
-  <si>
-    <t>LIC. NOJO</t>
-  </si>
-  <si>
     <t>AMAMENTAÇÃO</t>
   </si>
   <si>
@@ -152,12 +137,33 @@
   <si>
     <t>DIA (08:00 - 20:00)</t>
   </si>
+  <si>
+    <t>EIP (Extra Equipa)</t>
+  </si>
+  <si>
+    <t>OPTEL (Extra Equipa)</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>DISPENSA</t>
+  </si>
+  <si>
+    <t>ou</t>
+  </si>
+  <si>
+    <t>FALTAS</t>
+  </si>
+  <si>
+    <t>LICENÇAS: PARENTAL/CASAMENTO/NOJO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,8 +244,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,8 +357,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE65100"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5D4037"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -719,11 +758,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -812,15 +862,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -836,6 +877,84 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -883,88 +1002,43 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1428,300 +1502,300 @@
     <row r="2" spans="2:38" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:38" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="73"/>
-      <c r="AA4" s="73"/>
-      <c r="AB4" s="73"/>
-      <c r="AC4" s="73"/>
-      <c r="AD4" s="73"/>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="73"/>
-      <c r="AH4" s="73"/>
-      <c r="AI4" s="73"/>
-      <c r="AJ4" s="73"/>
-      <c r="AK4" s="73"/>
-      <c r="AL4" s="73"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39"/>
+      <c r="X4" s="39"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="39"/>
+      <c r="AB4" s="39"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="39"/>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="39"/>
     </row>
     <row r="5" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="73"/>
-      <c r="U5" s="73"/>
-      <c r="V5" s="73"/>
-      <c r="W5" s="73"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="73"/>
-      <c r="Z5" s="73"/>
-      <c r="AA5" s="73"/>
-      <c r="AB5" s="73"/>
-      <c r="AC5" s="73"/>
-      <c r="AD5" s="73"/>
-      <c r="AE5" s="73"/>
-      <c r="AF5" s="73"/>
-      <c r="AG5" s="73"/>
-      <c r="AH5" s="73"/>
-      <c r="AI5" s="73"/>
-      <c r="AJ5" s="73"/>
-      <c r="AK5" s="73"/>
-      <c r="AL5" s="73"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="39"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="39"/>
+      <c r="AA5" s="39"/>
+      <c r="AB5" s="39"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
     </row>
     <row r="6" spans="2:38" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="74"/>
-      <c r="S7" s="74"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="74"/>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74"/>
-      <c r="X7" s="74"/>
-      <c r="Y7" s="74"/>
-      <c r="Z7" s="74"/>
-      <c r="AA7" s="74"/>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="74"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="74"/>
-      <c r="AF7" s="74"/>
-      <c r="AG7" s="74"/>
-      <c r="AH7" s="74"/>
-      <c r="AI7" s="74"/>
-      <c r="AJ7" s="74"/>
-      <c r="AK7" s="74"/>
-      <c r="AL7" s="74"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
     </row>
     <row r="8" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74"/>
-      <c r="X8" s="74"/>
-      <c r="Y8" s="74"/>
-      <c r="Z8" s="74"/>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="74"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="74"/>
-      <c r="AF8" s="74"/>
-      <c r="AG8" s="74"/>
-      <c r="AH8" s="74"/>
-      <c r="AI8" s="74"/>
-      <c r="AJ8" s="74"/>
-      <c r="AK8" s="74"/>
-      <c r="AL8" s="74"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="40"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="40"/>
+      <c r="AL8" s="40"/>
     </row>
     <row r="9" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="77" t="s">
+      <c r="C10" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="77" t="s">
+      <c r="D10" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="35"/>
-      <c r="AL10" s="79" t="s">
+      <c r="F10" s="58"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="32"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="32"/>
+      <c r="AI10" s="32"/>
+      <c r="AJ10" s="32"/>
+      <c r="AK10" s="32"/>
+      <c r="AL10" s="47" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B11" s="76"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="36"/>
-      <c r="AE11" s="36"/>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="36"/>
-      <c r="AH11" s="36"/>
-      <c r="AI11" s="36"/>
-      <c r="AJ11" s="36"/>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="80"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="48"/>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="65"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="65"/>
-      <c r="W12" s="65"/>
-      <c r="X12" s="65"/>
-      <c r="Y12" s="65"/>
-      <c r="Z12" s="65"/>
-      <c r="AA12" s="65"/>
-      <c r="AB12" s="65"/>
-      <c r="AC12" s="65"/>
-      <c r="AD12" s="65"/>
-      <c r="AE12" s="65"/>
-      <c r="AF12" s="65"/>
-      <c r="AG12" s="65"/>
-      <c r="AH12" s="65"/>
-      <c r="AI12" s="65"/>
-      <c r="AJ12" s="65"/>
-      <c r="AK12" s="65"/>
-      <c r="AL12" s="66"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="50"/>
+      <c r="AE12" s="50"/>
+      <c r="AF12" s="50"/>
+      <c r="AG12" s="50"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="50"/>
+      <c r="AK12" s="50"/>
+      <c r="AL12" s="51"/>
     </row>
     <row r="13" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B13" s="13"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="62"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
@@ -1759,8 +1833,8 @@
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="61"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="42"/>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -1798,8 +1872,8 @@
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="61"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -1837,8 +1911,8 @@
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="61"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -1876,8 +1950,8 @@
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="61"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -1915,8 +1989,8 @@
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="61"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -1954,8 +2028,8 @@
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="61"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="42"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -1993,8 +2067,8 @@
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="61"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="42"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -2032,8 +2106,8 @@
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="61"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="42"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
@@ -2071,8 +2145,8 @@
       <c r="B22" s="16"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="42"/>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -2110,8 +2184,8 @@
       <c r="B23" s="16"/>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="61"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="42"/>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
@@ -2149,8 +2223,8 @@
       <c r="B24" s="16"/>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="61"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
@@ -2188,8 +2262,8 @@
       <c r="B25" s="16"/>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="61"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="42"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -2227,8 +2301,8 @@
       <c r="B26" s="16"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
@@ -2266,8 +2340,8 @@
       <c r="B27" s="16"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="61"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="42"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -2305,8 +2379,8 @@
       <c r="B28" s="16"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="61"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
@@ -2344,8 +2418,8 @@
       <c r="B29" s="16"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="61"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="42"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
@@ -2383,8 +2457,8 @@
       <c r="B30" s="16"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="61"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
@@ -2422,8 +2496,8 @@
       <c r="B31" s="16"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
       <c r="G31" s="17"/>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
@@ -2461,8 +2535,8 @@
       <c r="B32" s="19"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="61"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="42"/>
       <c r="G32" s="20"/>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
@@ -2497,52 +2571,52 @@
       <c r="AL32" s="21"/>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
+      <c r="B33" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="65"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="65"/>
-      <c r="K33" s="65"/>
-      <c r="L33" s="65"/>
-      <c r="M33" s="65"/>
-      <c r="N33" s="65"/>
-      <c r="O33" s="65"/>
-      <c r="P33" s="65"/>
-      <c r="Q33" s="65"/>
-      <c r="R33" s="65"/>
-      <c r="S33" s="65"/>
-      <c r="T33" s="65"/>
-      <c r="U33" s="65"/>
-      <c r="V33" s="65"/>
-      <c r="W33" s="65"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="65"/>
-      <c r="Z33" s="65"/>
-      <c r="AA33" s="65"/>
-      <c r="AB33" s="65"/>
-      <c r="AC33" s="65"/>
-      <c r="AD33" s="65"/>
-      <c r="AE33" s="65"/>
-      <c r="AF33" s="65"/>
-      <c r="AG33" s="65"/>
-      <c r="AH33" s="65"/>
-      <c r="AI33" s="65"/>
-      <c r="AJ33" s="65"/>
-      <c r="AK33" s="65"/>
-      <c r="AL33" s="66"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="50"/>
+      <c r="W33" s="50"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="50"/>
+      <c r="AA33" s="50"/>
+      <c r="AB33" s="50"/>
+      <c r="AC33" s="50"/>
+      <c r="AD33" s="50"/>
+      <c r="AE33" s="50"/>
+      <c r="AF33" s="50"/>
+      <c r="AG33" s="50"/>
+      <c r="AH33" s="50"/>
+      <c r="AI33" s="50"/>
+      <c r="AJ33" s="50"/>
+      <c r="AK33" s="50"/>
+      <c r="AL33" s="51"/>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="63"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="56"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -2580,8 +2654,8 @@
       <c r="B35" s="4"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="56"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
@@ -2619,8 +2693,8 @@
       <c r="B36" s="4"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="56"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
@@ -2658,8 +2732,8 @@
       <c r="B37" s="4"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="56"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -2697,8 +2771,8 @@
       <c r="B38" s="4"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="56"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
@@ -2736,8 +2810,8 @@
       <c r="B39" s="5"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="56"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -2772,52 +2846,52 @@
       <c r="AL39" s="12"/>
     </row>
     <row r="40" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B40" s="64" t="s">
+      <c r="B40" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="65"/>
-      <c r="L40" s="65"/>
-      <c r="M40" s="65"/>
-      <c r="N40" s="65"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="65"/>
-      <c r="Q40" s="65"/>
-      <c r="R40" s="65"/>
-      <c r="S40" s="65"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="65"/>
-      <c r="W40" s="65"/>
-      <c r="X40" s="65"/>
-      <c r="Y40" s="65"/>
-      <c r="Z40" s="65"/>
-      <c r="AA40" s="65"/>
-      <c r="AB40" s="65"/>
-      <c r="AC40" s="65"/>
-      <c r="AD40" s="65"/>
-      <c r="AE40" s="65"/>
-      <c r="AF40" s="65"/>
-      <c r="AG40" s="65"/>
-      <c r="AH40" s="65"/>
-      <c r="AI40" s="65"/>
-      <c r="AJ40" s="65"/>
-      <c r="AK40" s="65"/>
-      <c r="AL40" s="66"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="50"/>
+      <c r="L40" s="50"/>
+      <c r="M40" s="50"/>
+      <c r="N40" s="50"/>
+      <c r="O40" s="50"/>
+      <c r="P40" s="50"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="50"/>
+      <c r="S40" s="50"/>
+      <c r="T40" s="50"/>
+      <c r="U40" s="50"/>
+      <c r="V40" s="50"/>
+      <c r="W40" s="50"/>
+      <c r="X40" s="50"/>
+      <c r="Y40" s="50"/>
+      <c r="Z40" s="50"/>
+      <c r="AA40" s="50"/>
+      <c r="AB40" s="50"/>
+      <c r="AC40" s="50"/>
+      <c r="AD40" s="50"/>
+      <c r="AE40" s="50"/>
+      <c r="AF40" s="50"/>
+      <c r="AG40" s="50"/>
+      <c r="AH40" s="50"/>
+      <c r="AI40" s="50"/>
+      <c r="AJ40" s="50"/>
+      <c r="AK40" s="50"/>
+      <c r="AL40" s="51"/>
     </row>
     <row r="41" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="63"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="56"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -2855,8 +2929,8 @@
       <c r="B42" s="4"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="56"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
@@ -2894,8 +2968,8 @@
       <c r="B43" s="4"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="56"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
@@ -2933,8 +3007,8 @@
       <c r="B44" s="4"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="56"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
@@ -2972,8 +3046,8 @@
       <c r="B45" s="5"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="56"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -3008,52 +3082,52 @@
       <c r="AL45" s="12"/>
     </row>
     <row r="46" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B46" s="64" t="s">
+      <c r="B46" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="65"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="65"/>
-      <c r="N46" s="65"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="65"/>
-      <c r="R46" s="65"/>
-      <c r="S46" s="65"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="65"/>
-      <c r="X46" s="65"/>
-      <c r="Y46" s="65"/>
-      <c r="Z46" s="65"/>
-      <c r="AA46" s="65"/>
-      <c r="AB46" s="65"/>
-      <c r="AC46" s="65"/>
-      <c r="AD46" s="65"/>
-      <c r="AE46" s="65"/>
-      <c r="AF46" s="65"/>
-      <c r="AG46" s="65"/>
-      <c r="AH46" s="65"/>
-      <c r="AI46" s="65"/>
-      <c r="AJ46" s="65"/>
-      <c r="AK46" s="65"/>
-      <c r="AL46" s="66"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="50"/>
+      <c r="L46" s="50"/>
+      <c r="M46" s="50"/>
+      <c r="N46" s="50"/>
+      <c r="O46" s="50"/>
+      <c r="P46" s="50"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50"/>
+      <c r="S46" s="50"/>
+      <c r="T46" s="50"/>
+      <c r="U46" s="50"/>
+      <c r="V46" s="50"/>
+      <c r="W46" s="50"/>
+      <c r="X46" s="50"/>
+      <c r="Y46" s="50"/>
+      <c r="Z46" s="50"/>
+      <c r="AA46" s="50"/>
+      <c r="AB46" s="50"/>
+      <c r="AC46" s="50"/>
+      <c r="AD46" s="50"/>
+      <c r="AE46" s="50"/>
+      <c r="AF46" s="50"/>
+      <c r="AG46" s="50"/>
+      <c r="AH46" s="50"/>
+      <c r="AI46" s="50"/>
+      <c r="AJ46" s="50"/>
+      <c r="AK46" s="50"/>
+      <c r="AL46" s="51"/>
     </row>
     <row r="47" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="63"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="56"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -3091,8 +3165,8 @@
       <c r="B48" s="4"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="56"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
@@ -3130,8 +3204,8 @@
       <c r="B49" s="4"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="56"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
@@ -3169,8 +3243,8 @@
       <c r="B50" s="4"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="56"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
@@ -3208,8 +3282,8 @@
       <c r="B51" s="5"/>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="56"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
@@ -3244,52 +3318,52 @@
       <c r="AL51" s="12"/>
     </row>
     <row r="52" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B52" s="64" t="s">
+      <c r="B52" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C52" s="65"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
-      <c r="N52" s="65"/>
-      <c r="O52" s="65"/>
-      <c r="P52" s="65"/>
-      <c r="Q52" s="65"/>
-      <c r="R52" s="65"/>
-      <c r="S52" s="65"/>
-      <c r="T52" s="65"/>
-      <c r="U52" s="65"/>
-      <c r="V52" s="65"/>
-      <c r="W52" s="65"/>
-      <c r="X52" s="65"/>
-      <c r="Y52" s="65"/>
-      <c r="Z52" s="65"/>
-      <c r="AA52" s="65"/>
-      <c r="AB52" s="65"/>
-      <c r="AC52" s="65"/>
-      <c r="AD52" s="65"/>
-      <c r="AE52" s="65"/>
-      <c r="AF52" s="65"/>
-      <c r="AG52" s="65"/>
-      <c r="AH52" s="65"/>
-      <c r="AI52" s="65"/>
-      <c r="AJ52" s="65"/>
-      <c r="AK52" s="65"/>
-      <c r="AL52" s="66"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="50"/>
+      <c r="K52" s="50"/>
+      <c r="L52" s="50"/>
+      <c r="M52" s="50"/>
+      <c r="N52" s="50"/>
+      <c r="O52" s="50"/>
+      <c r="P52" s="50"/>
+      <c r="Q52" s="50"/>
+      <c r="R52" s="50"/>
+      <c r="S52" s="50"/>
+      <c r="T52" s="50"/>
+      <c r="U52" s="50"/>
+      <c r="V52" s="50"/>
+      <c r="W52" s="50"/>
+      <c r="X52" s="50"/>
+      <c r="Y52" s="50"/>
+      <c r="Z52" s="50"/>
+      <c r="AA52" s="50"/>
+      <c r="AB52" s="50"/>
+      <c r="AC52" s="50"/>
+      <c r="AD52" s="50"/>
+      <c r="AE52" s="50"/>
+      <c r="AF52" s="50"/>
+      <c r="AG52" s="50"/>
+      <c r="AH52" s="50"/>
+      <c r="AI52" s="50"/>
+      <c r="AJ52" s="50"/>
+      <c r="AK52" s="50"/>
+      <c r="AL52" s="51"/>
     </row>
     <row r="53" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
-      <c r="E53" s="62"/>
-      <c r="F53" s="63"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="56"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
@@ -3327,8 +3401,8 @@
       <c r="B54" s="4"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="56"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
@@ -3366,8 +3440,8 @@
       <c r="B55" s="4"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="56"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -3405,8 +3479,8 @@
       <c r="B56" s="4"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="56"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -3444,8 +3518,8 @@
       <c r="B57" s="5"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="58"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="79"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="9"/>
@@ -3512,65 +3586,61 @@
       <c r="AJ58" s="2"/>
       <c r="AK58" s="2"/>
     </row>
-    <row r="59" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B59" s="43" t="s">
+    <row r="59" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="44"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="45"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="59" t="s">
+      <c r="C59" s="67"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="68"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="59"/>
-      <c r="J59" s="59"/>
-      <c r="K59" s="59"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="38"/>
-      <c r="N59" s="59" t="s">
+      <c r="M59" s="35"/>
+      <c r="N59" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="O59" s="59"/>
-      <c r="P59" s="59"/>
-      <c r="Q59" s="59"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="52"/>
       <c r="R59" s="1"/>
-      <c r="S59" s="22" t="s">
-        <v>13</v>
+      <c r="S59" s="80"/>
+      <c r="T59" s="52" t="s">
+        <v>37</v>
       </c>
-      <c r="T59" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="U59" s="59"/>
-      <c r="V59" s="59"/>
-      <c r="W59" s="59"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="52"/>
+      <c r="W59" s="52"/>
       <c r="X59" s="1"/>
-      <c r="Y59" s="81" t="s">
+      <c r="Y59" s="81"/>
+      <c r="Z59" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="Z59" s="59" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA59" s="59"/>
-      <c r="AB59" s="59"/>
-      <c r="AC59" s="59"/>
+      <c r="AA59" s="52"/>
+      <c r="AB59" s="52"/>
+      <c r="AC59" s="52"/>
       <c r="AD59" s="2"/>
-      <c r="AE59" s="40" t="s">
+      <c r="AE59" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="AF59" s="41"/>
-      <c r="AG59" s="41"/>
-      <c r="AH59" s="41"/>
-      <c r="AI59" s="41"/>
-      <c r="AJ59" s="41"/>
-      <c r="AK59" s="41"/>
-      <c r="AL59" s="42"/>
+      <c r="AF59" s="64"/>
+      <c r="AG59" s="64"/>
+      <c r="AH59" s="64"/>
+      <c r="AI59" s="64"/>
+      <c r="AJ59" s="64"/>
+      <c r="AK59" s="64"/>
+      <c r="AL59" s="65"/>
     </row>
     <row r="60" spans="2:38" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="46"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="48"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="71"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -3602,52 +3672,52 @@
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
       <c r="AK60" s="2"/>
-      <c r="AL60" s="33"/>
+      <c r="AL60" s="30"/>
     </row>
     <row r="61" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B61" s="46"/>
-      <c r="C61" s="47"/>
-      <c r="D61" s="47"/>
-      <c r="E61" s="48"/>
-      <c r="G61" s="23" t="s">
+      <c r="B61" s="69"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="71"/>
+      <c r="G61" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" s="52"/>
+      <c r="J61" s="52"/>
+      <c r="K61" s="52"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="59" t="s">
-        <v>41</v>
+      <c r="N61" s="52" t="s">
+        <v>36</v>
       </c>
-      <c r="I61" s="59"/>
-      <c r="J61" s="59"/>
-      <c r="K61" s="59"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="24" t="s">
+      <c r="O61" s="52"/>
+      <c r="P61" s="52"/>
+      <c r="Q61" s="52"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N61" s="59" t="s">
+      <c r="T61" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="U61" s="52"/>
+      <c r="V61" s="52"/>
+      <c r="W61" s="52"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z61" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="O61" s="59"/>
-      <c r="P61" s="59"/>
-      <c r="Q61" s="59"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="T61" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="U61" s="59"/>
-      <c r="V61" s="59"/>
-      <c r="W61" s="59"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z61" s="59" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA61" s="59"/>
-      <c r="AB61" s="59"/>
-      <c r="AC61" s="59"/>
+      <c r="AA61" s="52"/>
+      <c r="AB61" s="52"/>
+      <c r="AC61" s="52"/>
       <c r="AD61" s="2"/>
       <c r="AE61" s="6"/>
       <c r="AF61" s="2"/>
@@ -3656,13 +3726,13 @@
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
       <c r="AK61" s="2"/>
-      <c r="AL61" s="33"/>
+      <c r="AL61" s="30"/>
     </row>
     <row r="62" spans="2:38" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="30"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="32"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="84"/>
+      <c r="D62" s="84"/>
+      <c r="E62" s="85"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -3694,54 +3764,54 @@
       <c r="AI62" s="2"/>
       <c r="AJ62" s="2"/>
       <c r="AK62" s="2"/>
-      <c r="AL62" s="33"/>
+      <c r="AL62" s="30"/>
     </row>
     <row r="63" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B63" s="49" t="s">
+      <c r="B63" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C63" s="50"/>
-      <c r="D63" s="50"/>
-      <c r="E63" s="51"/>
-      <c r="G63" s="26" t="s">
+      <c r="C63" s="73"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="74"/>
+      <c r="G63" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" s="52"/>
+      <c r="J63" s="52"/>
+      <c r="K63" s="52"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="N63" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="O63" s="52"/>
+      <c r="P63" s="52"/>
+      <c r="Q63" s="52"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="T63" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="U63" s="52"/>
+      <c r="V63" s="52"/>
+      <c r="W63" s="52"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="H63" s="59" t="s">
+      <c r="Z63" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I63" s="59"/>
-      <c r="J63" s="59"/>
-      <c r="K63" s="59"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="N63" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="O63" s="59"/>
-      <c r="P63" s="59"/>
-      <c r="Q63" s="59"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="T63" s="59" t="s">
-        <v>33</v>
-      </c>
-      <c r="U63" s="59"/>
-      <c r="V63" s="59"/>
-      <c r="W63" s="59"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z63" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA63" s="59"/>
-      <c r="AB63" s="59"/>
-      <c r="AC63" s="59"/>
+      <c r="AA63" s="52"/>
+      <c r="AB63" s="52"/>
+      <c r="AC63" s="52"/>
       <c r="AD63" s="2"/>
       <c r="AE63" s="6"/>
       <c r="AF63" s="2"/>
@@ -3750,13 +3820,13 @@
       <c r="AI63" s="2"/>
       <c r="AJ63" s="2"/>
       <c r="AK63" s="2"/>
-      <c r="AL63" s="33"/>
+      <c r="AL63" s="30"/>
     </row>
     <row r="64" spans="2:38" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="30"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="32"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="84"/>
+      <c r="D64" s="84"/>
+      <c r="E64" s="85"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -3788,52 +3858,56 @@
       <c r="AI64" s="2"/>
       <c r="AJ64" s="2"/>
       <c r="AK64" s="2"/>
-      <c r="AL64" s="33"/>
+      <c r="AL64" s="30"/>
     </row>
     <row r="65" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B65" s="52"/>
-      <c r="C65" s="53"/>
-      <c r="D65" s="53"/>
-      <c r="E65" s="54"/>
+      <c r="B65" s="75"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="76"/>
+      <c r="E65" s="77"/>
       <c r="G65" s="27" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
-      <c r="H65" s="59" t="s">
-        <v>35</v>
+      <c r="H65" s="52" t="s">
+        <v>31</v>
       </c>
-      <c r="I65" s="59"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="59"/>
+      <c r="I65" s="52"/>
+      <c r="J65" s="52"/>
+      <c r="K65" s="52"/>
       <c r="L65" s="1"/>
       <c r="M65" s="27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
-      <c r="N65" s="59" t="s">
-        <v>34</v>
+      <c r="N65" s="86" t="s">
+        <v>41</v>
       </c>
-      <c r="O65" s="59"/>
-      <c r="P65" s="59"/>
-      <c r="Q65" s="59"/>
+      <c r="O65" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q65" s="88"/>
       <c r="R65" s="1"/>
       <c r="S65" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="T65" s="59" t="s">
-        <v>35</v>
+      <c r="T65" s="89" t="s">
+        <v>22</v>
       </c>
-      <c r="U65" s="59"/>
-      <c r="V65" s="59"/>
-      <c r="W65" s="59"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="27" t="s">
+      <c r="U65" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="Z65" s="59" t="s">
-        <v>36</v>
+      <c r="V65" s="87" t="s">
+        <v>43</v>
       </c>
-      <c r="AA65" s="59"/>
-      <c r="AB65" s="59"/>
-      <c r="AC65" s="59"/>
+      <c r="W65" s="90"/>
+      <c r="X65" s="90"/>
+      <c r="Y65" s="90"/>
+      <c r="Z65" s="90"/>
+      <c r="AA65" s="90"/>
+      <c r="AB65" s="90"/>
+      <c r="AC65" s="88"/>
       <c r="AD65" s="2"/>
       <c r="AE65" s="28"/>
       <c r="AF65" s="29"/>
@@ -3842,7 +3916,7 @@
       <c r="AI65" s="29"/>
       <c r="AJ65" s="29"/>
       <c r="AK65" s="29"/>
-      <c r="AL65" s="34"/>
+      <c r="AL65" s="31"/>
     </row>
     <row r="66" spans="2:38" x14ac:dyDescent="0.25">
       <c r="G66" s="2"/>
@@ -3865,7 +3939,7 @@
       <c r="X66" s="2"/>
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
-      <c r="AA66" s="82"/>
+      <c r="AA66" s="38"/>
       <c r="AB66" s="2"/>
       <c r="AC66" s="2"/>
       <c r="AD66" s="2"/>
@@ -17540,26 +17614,44 @@
       <c r="AK480" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="B4:AL5"/>
-    <mergeCell ref="B7:AL8"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="AL10:AL11"/>
-    <mergeCell ref="B12:AL12"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="H63:K63"/>
-    <mergeCell ref="Z61:AC61"/>
-    <mergeCell ref="Z63:AC63"/>
-    <mergeCell ref="H59:K59"/>
-    <mergeCell ref="N59:Q59"/>
+  <mergeCells count="72">
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="V65:AC65"/>
+    <mergeCell ref="AE59:AL59"/>
+    <mergeCell ref="B59:E61"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="N61:Q61"/>
+    <mergeCell ref="N63:Q63"/>
+    <mergeCell ref="T61:W61"/>
+    <mergeCell ref="T63:W63"/>
+    <mergeCell ref="H65:K65"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B33:AL33"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E10:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="B40:AL40"/>
+    <mergeCell ref="B46:AL46"/>
+    <mergeCell ref="B52:AL52"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="T59:W59"/>
@@ -17576,44 +17668,25 @@
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="B40:AL40"/>
-    <mergeCell ref="B46:AL46"/>
-    <mergeCell ref="B52:AL52"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E10:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B33:AL33"/>
-    <mergeCell ref="AE59:AL59"/>
-    <mergeCell ref="B59:E61"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="Z65:AC65"/>
-    <mergeCell ref="N61:Q61"/>
-    <mergeCell ref="N63:Q63"/>
-    <mergeCell ref="N65:Q65"/>
-    <mergeCell ref="T61:W61"/>
-    <mergeCell ref="T63:W63"/>
-    <mergeCell ref="T65:W65"/>
-    <mergeCell ref="H65:K65"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="Z61:AC61"/>
+    <mergeCell ref="Z63:AC63"/>
+    <mergeCell ref="H59:K59"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="B4:AL5"/>
+    <mergeCell ref="B7:AL8"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="AL10:AL11"/>
+    <mergeCell ref="B12:AL12"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
